--- a/نشاط تحليل البيانات.xlsx
+++ b/نشاط تحليل البيانات.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba1d93a2b8fd1233/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AF78E72-904C-4C40-B59F-CE6FA65B3CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{6CC93089-BAD1-4D25-9A08-4FFCD3D65BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{E0BDA989-6FBA-49D8-809C-B604B20C3337}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{E0BDA989-6FBA-49D8-809C-B604B20C3337}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
     <sheet name="ورقة2" sheetId="2" r:id="rId2"/>
     <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
+    <sheet name="ورقة4" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ورقة3!$G$1:$G$11</definedName>
@@ -43,8 +44,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
   <si>
     <t>رقم التسجيل</t>
   </si>
@@ -287,13 +310,40 @@
   </si>
   <si>
     <t>اجمالي المكالمات لقسم المبيعات</t>
+  </si>
+  <si>
+    <t>جدول الطلاب</t>
+  </si>
+  <si>
+    <t>جدول الإنجاز</t>
+  </si>
+  <si>
+    <t>رقم الطالب</t>
+  </si>
+  <si>
+    <t>الصفحات</t>
+  </si>
+  <si>
+    <t>VLOOKUP(</t>
+  </si>
+  <si>
+    <t>XLOOKUP(</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>ترتيب الاسم</t>
+  </si>
+  <si>
+    <t>INDEX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,8 +400,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,8 +441,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -514,11 +597,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -568,13 +748,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -588,33 +767,83 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -723,89 +952,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="medium">
           <color rgb="FFCCCCCC"/>
@@ -947,6 +1093,41 @@
         <left style="medium">
           <color rgb="FFCCCCCC"/>
         </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
         <right/>
         <top style="medium">
           <color rgb="FFCCCCCC"/>
@@ -967,13 +1148,94 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
         <bottom style="medium">
           <color rgb="FFCCCCCC"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -1020,58 +1282,6 @@
           <color rgb="FFCCCCCC"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
     </dxf>
     <dxf>
       <font>
@@ -1301,6 +1511,55 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1329,36 +1588,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1373,19 +1602,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FAB7B4DF-B6E0-4BD0-925D-083BF1C33D9C}" name="الجدول1" displayName="الجدول1" ref="A1:I16" totalsRowShown="0" headerRowDxfId="25" dataDxfId="17" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FAB7B4DF-B6E0-4BD0-925D-083BF1C33D9C}" name="الجدول1" displayName="الجدول1" ref="A1:I16" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="A1:I16" xr:uid="{FAB7B4DF-B6E0-4BD0-925D-083BF1C33D9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E16">
     <sortCondition descending="1" ref="E1:E20"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C2309B5E-AE22-4DAF-86A6-C1A14EC4AE3D}" name="رقم التسجيل" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{47447181-5769-4048-9375-33D39D5B2BF0}" name="الاسم" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{695F3275-0F77-4A3C-9940-A670E5C94A55}" name="المدن" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{D010606B-2B96-4C73-A72E-F2BEBF178A4F}" name="الجوال" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{C2D6DAC4-F2FC-444B-BE69-8F8EBEE04424}" name="عدد الكتب المطلوبة" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{245B2706-5EEA-4DA3-8D78-0140A853323B}" name="الاسم الأول" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{DDBA2E87-5849-4BF6-892D-47FC01718B12}" name="الاسم الثاني" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{C2309B5E-AE22-4DAF-86A6-C1A14EC4AE3D}" name="رقم التسجيل" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{47447181-5769-4048-9375-33D39D5B2BF0}" name="الاسم" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{695F3275-0F77-4A3C-9940-A670E5C94A55}" name="المدن" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{D010606B-2B96-4C73-A72E-F2BEBF178A4F}" name="الجوال" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{C2D6DAC4-F2FC-444B-BE69-8F8EBEE04424}" name="عدد الكتب المطلوبة" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{245B2706-5EEA-4DA3-8D78-0140A853323B}" name="الاسم الأول" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{DDBA2E87-5849-4BF6-892D-47FC01718B12}" name="الاسم الثاني" dataDxfId="17"/>
     <tableColumn id="9" xr3:uid="{575AB40A-19AA-4E0B-9D35-54E65C2822FF}" name="المدن2" dataDxfId="16"/>
     <tableColumn id="10" xr3:uid="{21BD5B35-B200-4447-8A94-D1F3DB3A19A4}" name="الكتب المطلوبة" dataDxfId="15"/>
   </tableColumns>
@@ -1394,7 +1623,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB5C55FE-7091-4A34-8431-2146F409E239}" name="الجدول2" displayName="الجدول2" ref="A1:H17" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB5C55FE-7091-4A34-8431-2146F409E239}" name="الجدول2" displayName="الجدول2" ref="A1:H17" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:H17" xr:uid="{BB5C55FE-7091-4A34-8431-2146F409E239}">
     <filterColumn colId="5">
       <customFilters>
@@ -1406,13 +1635,13 @@
     <sortCondition descending="1" ref="F1:F21"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{32B36291-6F0B-4EDE-821F-D9164E41DFD9}" name="رقم العضوية" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DFA66003-ABCD-4FE8-8D54-913D873A922D}" name="الاسم الكامل" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{0229CE1E-7707-42A7-9A03-FFB1060F5F6D}" name="الاسم الأخير" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{DFD11680-BAAA-464B-92FB-59EF21ACD1A1}" name="نوع الاشتراك" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{0EA18579-5785-486F-A1A7-C54EBB5EFB2C}" name="الجوال" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{71F88878-3EC5-45FB-88E1-3A9B72A133EE}" name="عدد الزيارات" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{0B211F2F-B91F-4379-8CE3-DD7E45A0779E}" name="الاسم الأول" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{32B36291-6F0B-4EDE-821F-D9164E41DFD9}" name="رقم العضوية" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{DFA66003-ABCD-4FE8-8D54-913D873A922D}" name="الاسم الكامل" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{0229CE1E-7707-42A7-9A03-FFB1060F5F6D}" name="الاسم الأخير" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{DFD11680-BAAA-464B-92FB-59EF21ACD1A1}" name="نوع الاشتراك" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{0EA18579-5785-486F-A1A7-C54EBB5EFB2C}" name="الجوال" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{71F88878-3EC5-45FB-88E1-3A9B72A133EE}" name="عدد الزيارات" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{0B211F2F-B91F-4379-8CE3-DD7E45A0779E}" name="الاسم الأول" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{975C8E59-EC9C-4EE8-A089-AF938A00FD61}" name="نوع الاشتراك3" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2659,470 +2888,461 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="32"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>180</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>0.95</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="19">
         <v>4</v>
       </c>
-      <c r="F2" s="21" t="str">
+      <c r="F2" s="20" t="str">
         <f>IF(D2&gt;=90%,"متميز","يحتاج تطوير")</f>
         <v>متميز</v>
       </c>
-      <c r="G2" s="21" t="str">
+      <c r="G2" s="20" t="str">
         <f>IF(AND(C2&gt;=150,D2&gt;=90%),"يستحق المكافأة","لايستحق المكافأه")</f>
         <v>يستحق المكافأة</v>
       </c>
-      <c r="H2" s="21" t="str">
+      <c r="H2" s="20" t="str">
         <f>IF(OR(E2&gt;=5,D2&gt;=97%),"مرشح","غير مرشح")</f>
         <v>غير مرشح</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="29">
         <f>C2/E2</f>
         <v>45</v>
       </c>
-      <c r="J2" s="33"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="19">
         <v>120</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>0.88</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="19">
         <v>2</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="20" t="str">
         <f t="shared" ref="F3:F11" si="0">IF(D3&gt;=90%,"متميز","يحتاج تطوير")</f>
         <v>يحتاج تطوير</v>
       </c>
-      <c r="G3" s="21" t="str">
+      <c r="G3" s="20" t="str">
         <f t="shared" ref="G3:G11" si="1">IF(AND(C3&gt;=150,D3&gt;=90%),"يستحق المكافأة","لايستحق المكافأه")</f>
         <v>لايستحق المكافأه</v>
       </c>
-      <c r="H3" s="21" t="str">
+      <c r="H3" s="20" t="str">
         <f t="shared" ref="H3:H11" si="2">IF(OR(E3&gt;=5,D3&gt;=97%),"مرشح","غير مرشح")</f>
         <v>غير مرشح</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="29">
         <f>C3/E3</f>
         <v>60</v>
       </c>
-      <c r="J3" s="33"/>
+      <c r="J3" s="28"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="19">
         <v>210</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>0.97</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
         <v>5</v>
       </c>
-      <c r="F4" s="21" t="str">
+      <c r="F4" s="20" t="str">
         <f t="shared" si="0"/>
         <v>متميز</v>
       </c>
-      <c r="G4" s="21" t="str">
+      <c r="G4" s="20" t="str">
         <f t="shared" si="1"/>
         <v>يستحق المكافأة</v>
       </c>
-      <c r="H4" s="21" t="str">
+      <c r="H4" s="20" t="str">
         <f t="shared" si="2"/>
         <v>مرشح</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <f t="shared" ref="I4:I11" si="3">C4/E4</f>
         <v>42</v>
       </c>
-      <c r="J4" s="33"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>90</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>0.85</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="21" t="str">
+      <c r="F5" s="20" t="str">
         <f t="shared" si="0"/>
         <v>يحتاج تطوير</v>
       </c>
-      <c r="G5" s="21" t="str">
+      <c r="G5" s="20" t="str">
         <f t="shared" si="1"/>
         <v>لايستحق المكافأه</v>
       </c>
-      <c r="H5" s="21" t="str">
+      <c r="H5" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="29">
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="J5" s="33"/>
+      <c r="J5" s="28"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>160</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>0.92</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>3</v>
       </c>
-      <c r="F6" s="21" t="str">
+      <c r="F6" s="20" t="str">
         <f t="shared" si="0"/>
         <v>متميز</v>
       </c>
-      <c r="G6" s="21" t="str">
+      <c r="G6" s="20" t="str">
         <f t="shared" si="1"/>
         <v>يستحق المكافأة</v>
       </c>
-      <c r="H6" s="21" t="str">
+      <c r="H6" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="29">
         <f t="shared" si="3"/>
         <v>53.333333333333336</v>
       </c>
-      <c r="J6" s="33"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>140</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>0.89</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="str">
+      <c r="F7" s="20" t="str">
         <f t="shared" si="0"/>
         <v>يحتاج تطوير</v>
       </c>
-      <c r="G7" s="21" t="str">
+      <c r="G7" s="20" t="str">
         <f t="shared" si="1"/>
         <v>لايستحق المكافأه</v>
       </c>
-      <c r="H7" s="21" t="str">
+      <c r="H7" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="29">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="J7" s="33"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>220</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>0.98</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>6</v>
       </c>
-      <c r="F8" s="21" t="str">
+      <c r="F8" s="20" t="str">
         <f t="shared" si="0"/>
         <v>متميز</v>
       </c>
-      <c r="G8" s="21" t="str">
+      <c r="G8" s="20" t="str">
         <f t="shared" si="1"/>
         <v>يستحق المكافأة</v>
       </c>
-      <c r="H8" s="21" t="str">
+      <c r="H8" s="20" t="str">
         <f t="shared" si="2"/>
         <v>مرشح</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="29">
         <f t="shared" si="3"/>
         <v>36.666666666666664</v>
       </c>
-      <c r="J8" s="33"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>100</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>0.8</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="str">
+      <c r="F9" s="20" t="str">
         <f t="shared" si="0"/>
         <v>يحتاج تطوير</v>
       </c>
-      <c r="G9" s="21" t="str">
+      <c r="G9" s="20" t="str">
         <f t="shared" si="1"/>
         <v>لايستحق المكافأه</v>
       </c>
-      <c r="H9" s="21" t="str">
+      <c r="H9" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="29">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="J9" s="33"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>175</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>0.94</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>4</v>
       </c>
-      <c r="F10" s="21" t="str">
+      <c r="F10" s="20" t="str">
         <f t="shared" si="0"/>
         <v>متميز</v>
       </c>
-      <c r="G10" s="21" t="str">
+      <c r="G10" s="20" t="str">
         <f t="shared" si="1"/>
         <v>يستحق المكافأة</v>
       </c>
-      <c r="H10" s="21" t="str">
+      <c r="H10" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="29">
         <f t="shared" si="3"/>
         <v>43.75</v>
       </c>
-      <c r="J10" s="33"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>130</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>0.91</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <v>3</v>
       </c>
-      <c r="F11" s="21" t="str">
+      <c r="F11" s="20" t="str">
         <f t="shared" si="0"/>
         <v>متميز</v>
       </c>
-      <c r="G11" s="21" t="str">
+      <c r="G11" s="20" t="str">
         <f t="shared" si="1"/>
         <v>لايستحق المكافأه</v>
       </c>
-      <c r="H11" s="21" t="str">
+      <c r="H11" s="20" t="str">
         <f t="shared" si="2"/>
         <v>غير مرشح</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="29">
         <f t="shared" si="3"/>
         <v>43.333333333333336</v>
       </c>
-      <c r="J11" s="33"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
     </row>
     <row r="17" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="21">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="20">
         <f>COUNTIF(F1:F11,F2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="21">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="20">
         <f>COUNTIFS(F1:F11,F2,B1:B11,B2)</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="21">
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="20">
         <f>SUMIF(B2:B11,B3,C2:C11)</f>
         <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="21">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="20">
         <f>SUMIF(B1:B11,B2,C1:C11)</f>
         <v>705</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="21">
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="20">
         <f>SUMIF(B2:B11,B5,C2:C11)</f>
         <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="21">
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="20">
         <f>SUMIFS(C2:C11,B2:B11,"الدعم الفني",D2:D11,"&gt;=90%")</f>
         <v>565</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
     </row>
   </sheetData>
   <autoFilter ref="G1:G11" xr:uid="{12A3FC91-37B0-444C-8D0B-495C3B7709D9}"/>
@@ -3135,4 +3355,246 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D89F0A-B7EF-4FAE-A216-0A943CBADF1D}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.4140625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="9.75" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="35"/>
+    </row>
+    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="38"/>
+      <c r="B2" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="35"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="35"/>
+    </row>
+    <row r="4" spans="1:7" ht="40.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="44"/>
+      <c r="E4" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="45"/>
+    </row>
+    <row r="5" spans="1:7" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="38"/>
+      <c r="B5" s="40">
+        <v>101</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="48">
+        <v>101</v>
+      </c>
+      <c r="F5" s="48">
+        <v>25</v>
+      </c>
+      <c r="G5" s="45"/>
+    </row>
+    <row r="6" spans="1:7" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="38"/>
+      <c r="B6" s="40">
+        <v>102</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="44"/>
+      <c r="E6" s="48">
+        <v>102</v>
+      </c>
+      <c r="F6" s="48">
+        <v>18</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="9" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+      <c r="A9" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="49">
+        <v>101</v>
+      </c>
+      <c r="C10" s="49" t="str">
+        <f>VLOOKUP(B10,B1:C6,2,FALSE)</f>
+        <v>أحمد</v>
+      </c>
+      <c r="D10" s="49">
+        <f>VLOOKUP(B10,E1:G6,2,FALSE)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="49">
+        <v>102</v>
+      </c>
+      <c r="C11" s="49" t="str">
+        <f t="shared" ref="C11:C12" si="0">VLOOKUP(B11,B2:C7,2,FALSE)</f>
+        <v>خالد</v>
+      </c>
+      <c r="D11" s="49">
+        <f>VLOOKUP(B11,E2:G7,2,FALSE)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+    </row>
+    <row r="14" spans="1:7" ht="23" x14ac:dyDescent="0.5">
+      <c r="A14" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="49">
+        <v>101</v>
+      </c>
+      <c r="C15" s="49" t="str">
+        <f>_xlfn.XLOOKUP(B15,B4:B6,C4:C6)</f>
+        <v>أحمد</v>
+      </c>
+      <c r="D15" s="49">
+        <f>_xlfn.XLOOKUP(B15,E4:E6,F4:F6)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="49">
+        <v>102</v>
+      </c>
+      <c r="C16" s="49" t="str">
+        <f>_xlfn.XLOOKUP(B16,B5:B7,C5:C7)</f>
+        <v>خالد</v>
+      </c>
+      <c r="D16" s="49">
+        <f>_xlfn.XLOOKUP(B16,E5:E7,F5:F7)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="49">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="49">
+        <f>MATCH(B20,C5:C6,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D21" s="51" cm="1">
+        <f t="array" ref="D21">INDEX(D9:D11,MATCH(1,(B9:B11=E20)*(C9:C11=D20),0))</f>
+        <v>18</v>
+      </c>
+      <c r="E21" s="51"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D22" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D21:E21"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D20" xr:uid="{D1E37917-4513-4A1C-BB32-6AC5A813BBB3}">
+      <formula1>$C$10:$C$11</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E20" xr:uid="{D0A4CFB9-5C2A-423D-8A80-05FC05064BAD}">
+      <formula1>$B$10:$B$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>